--- a/таблицы/U_testing_strategy.xlsx
+++ b/таблицы/U_testing_strategy.xlsx
@@ -440,18 +440,17 @@
     <row r="1" ht="17.35" customHeight="1" s="10">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>Стратегия тестирования — Task2 и модуль разбора сообщений сервера</t>
+          <t>Стратегия тестирования — Task2, Task3 и модуль разбора сообщений сервера (версия 2)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="10">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Автор: Голь Фёдор     Дата: 20.09.2026     Проект: StAlGoLM</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Автор: Голь Фёдор     Дата: 07.10.2026 (v1 — 20.09.2026)     Проект: StAlGoLM</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="18" customHeight="1" s="10">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -462,11 +461,10 @@
     <row r="5" ht="30" customHeight="1" s="10">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>Проверить корректность работы задания Task2 (метод Ньютона, вариант №6) и корректность разбора команд сервером — в частности, определение границы одного сообщения в потоке TCP-байт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+          <t>Проверить корректность работы заданий Task2 (метод Ньютона, вариант №6) и Task3 (метод половинного деления, вариант №3), корректность разбора команд сервером — в частности, определение границы одного сообщения в потоке TCP-байт — и отсутствие регрессий в остальных заданиях после слияния ветки Steph-Changes.</t>
+        </is>
+      </c>
+    </row>
     <row r="7" ht="18" customHeight="1" s="10">
       <c r="A7" s="13" t="inlineStr">
         <is>
@@ -477,11 +475,10 @@
     <row r="8" ht="42" customHeight="1" s="10">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>task2_generate() — математика и построение вариантов ответа; команда task2 &lt;1-10&gt; в диспетчере команд; таблица статистики StatisticTask2; разбор сообщений в mytcpserver.cpp (slotServerRead).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>task2_generate() и task3_generate() — математика и построение вариантов ответа; команды task2 &lt;1-10&gt; и task3 &lt;1-10&gt; в диспетчере команд; таблицы статистики StatisticTask2 и StatisticTask3; разбор сообщений в mytcpserver.cpp (slotServerRead); обновлённый help и границы номеров заданий.</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="18" customHeight="1" s="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
@@ -492,11 +489,10 @@
     <row r="11" ht="30" customHeight="1" s="10">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Клиентское приложение на Qt (UI); полное содержимое базы данных и роли администратора — это части задач других участников команды.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>Клиентский UI (проверяется вручную через оконный клиент и PuTTY); Docker/Doxygen — инфраструктура (работа Степана, проверяется его документацией); полное содержимое БД и роли администратора — часть задач других участников команды.</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="18" customHeight="1" s="10">
       <c r="A13" s="13" t="inlineStr">
         <is>
@@ -507,11 +503,10 @@
     <row r="14" ht="42" customHeight="1" s="10">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>Функциональное (happy path: регистрация → вход → задание → верный/неверный ответ); граничное и негативное (некорректные номера заданий, отсутствие авторизации); регрессионное (команды reg/auth/whoami/help по-прежнему работают после правки mytcpserver.cpp).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>Функциональное (happy path: регистрация → вход → задание → верный/неверный ответ); граничное и негативное (некорректные номера заданий 0/11, отсутствие авторизации); регрессионное (команды reg/auth/whoami/help и задания task1/task4 не сломаны после слияния); модульные тесты QtTest: Task2 — tests/task2tests.pro, Task3 — tests/task3tests.pro (по 200 случайных генераций на тест).</t>
+        </is>
+      </c>
+    </row>
     <row r="16" ht="18" customHeight="1" s="10">
       <c r="A16" s="13" t="inlineStr">
         <is>
@@ -522,11 +517,10 @@
     <row r="17" ht="55.5" customHeight="1" s="10">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>Ручная проверка через PuTTY (raw-соединение на localhost:33333) для разового исследования; повторяемые сценарии — через Python-скрипт с сокетами, чтобы можно было прогнать одну и ту же последовательность команд после каждого изменения кода; математика задания (формула Ньютона) сверялась вручную на бумаге для нескольких сгенерированных примеров.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
+          <t>Ручная проверка через PuTTY (raw-соединение на localhost:33333) и через оконный клиент для разового исследования; повторяемые сценарии — через Python-скрипт с сокетами, чтобы прогонять одну и ту же последовательность команд после каждого изменения кода; математика заданий сверяется вручную и покрывается модульными тестами.</t>
+        </is>
+      </c>
+    </row>
     <row r="19" ht="18" customHeight="1" s="10">
       <c r="A19" s="13" t="inlineStr">
         <is>
@@ -541,7 +535,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="18" customHeight="1" s="10">
       <c r="A22" s="13" t="inlineStr">
         <is>
@@ -552,7 +545,7 @@
     <row r="23" ht="30" customHeight="1" s="10">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>Все сценарии чек-листа на листе «Чек-лист» дают Pass; ранее работавшие команды (reg/auth/whoami/help/task1-4) не сломаны после изменений.</t>
+          <t>Все сценарии чек-листа на листе «Чек-лист» дают Pass; ранее работавшие команды (reg/auth/whoami/help) и задания task1/task4 не сломаны после слияния; тесты Task2 и Task3 дают 6 passed.</t>
         </is>
       </c>
     </row>
@@ -569,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="9" min="1" max="1"/>
@@ -927,34 +920,276 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" s="10">
-      <c r="A13" s="16" t="n">
-        <v>12</v>
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>task3</t>
+        </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>task1 1 (регрессия чужого задания)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
+          <t>error: usage: task3 &lt;1-10&gt;</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>Нет номера задания</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>task3 0</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>error: task number must be 1-10</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>Граничное значение снизу</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>task3 11</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>error: task number must be 1-10</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>Граничное значение сверху</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>task3 1 (без входа в аккаунт)</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>error: login required to use tasks</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>По аналогии с task1-2</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>task3 1 (после входа)</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
           <t>user</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>Текст задания Task1, как раньше</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
-        <is>
-          <t>Общий диспетчер задач не задет добавлением task2</t>
-        </is>
-      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>Текст задания: f(x), отрезок [a,b], epsilon, 4 варианта корня</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>Метод половинного деления (вариант №3)</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Ответ правильным номером варианта (task3)</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Верно! StatisticTask3[N] += 1 (...)</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Y |</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr"/>
+      <c r="F18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Ответ неправильным номером варианта (task3)</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Неверно! StatisticTask3[N] -= 1 (...). Правильный ответ: N</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Y |</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr"/>
+      <c r="F19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>mystats 3</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Статистика Task3: 10 ячеек с обновлёнными значениями</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>В Task3 десять шаблонов</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>help</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>В списке команд строка про task3 (bisection)</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>После слияния Steph-Changes</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>task1 1 и task4 1 (регрессия после слияния)</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Задания Task1/Task4 работают как раньше</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>Диспетчер и статистика не задеты</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
